--- a/GroceryApplication/src/test/resources/TestData.xlsx
+++ b/GroceryApplication/src/test/resources/TestData.xlsx
@@ -5,38 +5,32 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASHNA\eclipse-workspace\GroceryApplication\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASHNA\git\Groceryapprepo\GroceryApplication\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78520188-4AB4-4740-B34B-0B33B3F798FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B653A9-96FD-4A6A-B607-87C7B8C4C95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E014261F-3EB8-4077-A38C-17100BE87443}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E014261F-3EB8-4077-A38C-17100BE87443}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpage" sheetId="1" r:id="rId1"/>
     <sheet name="Managenews" sheetId="2" r:id="rId2"/>
     <sheet name="Adminusers" sheetId="3" r:id="rId3"/>
+    <sheet name="Managecategory" sheetId="4" r:id="rId4"/>
+    <sheet name="ManageContact" sheetId="5" r:id="rId5"/>
+    <sheet name="ManageFooterText" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>username</t>
   </si>
@@ -59,13 +53,43 @@
     <t>aqwerrt</t>
   </si>
   <si>
-    <t>discount sale</t>
-  </si>
-  <si>
-    <t>ashnamwer</t>
-  </si>
-  <si>
-    <t>ashnaaddglmn0</t>
+    <t>category</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>adress</t>
+  </si>
+  <si>
+    <t>delivery time</t>
+  </si>
+  <si>
+    <t>chargelimit</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>aghrham</t>
+  </si>
+  <si>
+    <t>pineapple</t>
+  </si>
+  <si>
+    <t>kollam</t>
+  </si>
+  <si>
+    <t>aoipchgk13401679@gmail.com</t>
+  </si>
+  <si>
+    <t>asl12kzwm@gmail.com</t>
+  </si>
+  <si>
+    <t>discount sale ends soon</t>
   </si>
 </sst>
 </file>
@@ -486,7 +510,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -509,13 +533,100 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{D9DDEAB9-D062-4D99-A326-A15D14F7BCC1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23BAB8AA-5D01-4A29-9B83-8CBFCCDA2320}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC41685A-637C-4A8E-A4BF-9D82AAFC2FAB}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98BD50B3-410D-432E-9E72-FA1228478A62}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{162A570B-6B95-40C8-8FEA-F0D1DBAA6868}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>